--- a/artfynd/A 7148-2023 artfynd.xlsx
+++ b/artfynd/A 7148-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119824873</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7148-2023 artfynd.xlsx
+++ b/artfynd/A 7148-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119824873</v>
+        <v>131732343</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Gartsbotjärn, Hls</t>
+          <t>Gartstjärnen Nord, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565804</v>
+        <v>566327</v>
       </c>
       <c r="R2" t="n">
-        <v>6849306</v>
+        <v>6849545</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,22 +754,1054 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131733092</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97308</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gartstjärnen Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566339</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6849554</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 m2</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131732849</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gartstjärnen Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566244</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6849499</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119824873</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>V Gartsbotjärn, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565804</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6849306</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119825377</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>V Gartsbotjärn, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566316</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6849554</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131731823</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Buberget Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>565984</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6849474</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131731825</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gartstjärnen Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566280</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6849554</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131731828</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gartstjärnen Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566321</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6849552</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131731831</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gartstjärnen Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566338</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6849542</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131738471</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gartstjärnen Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>566277</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6849554</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131738473</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gartstjärnen Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566318</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6849543</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7148-2023 artfynd.xlsx
+++ b/artfynd/A 7148-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732343</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732849</t>
         </is>
       </c>
     </row>
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119824873</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119825377</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731823</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731825</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731828</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731831</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738471</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,8 +1857,26 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738473</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>